--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484173_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484173_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>B. BORRERO PERLAZA</t>
+          <t>J. GAVALDA GUILLEN</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.767</v>
+        <v>0.7692</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.4429</v>
+        <v>1.568</v>
       </c>
       <c r="F2" t="n">
-        <v>1.2099</v>
+        <v>-0.7988</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.4505</v>
+        <v>0.2912</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.0529</v>
+        <v>-0.0507</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3977</v>
+        <v>0.342</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.2668</v>
+        <v>3.0077</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.3873</v>
+        <v>1.3508</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1205</v>
+        <v>1.6568</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.1837</v>
+        <v>-2.7164</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.6655</v>
+        <v>-1.4015</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.5182</v>
+        <v>-1.3149</v>
       </c>
       <c r="P2" t="n">
-        <v>0.3968</v>
+        <v>0.5952</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.9838</v>
+        <v>-0.9919</v>
       </c>
       <c r="R2" t="n">
-        <v>2.3806</v>
+        <v>1.5871</v>
       </c>
       <c r="S2" t="n">
-        <v>1.5548</v>
+        <v>-1.2002</v>
       </c>
       <c r="T2" t="n">
-        <v>1.5418</v>
+        <v>-0.4477</v>
       </c>
       <c r="U2" t="n">
-        <v>0.013</v>
+        <v>-0.7524999999999999</v>
       </c>
       <c r="V2" t="n">
-        <v>0.266</v>
+        <v>1.083</v>
       </c>
       <c r="W2" t="n">
-        <v>0.266</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.083</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>R. DIAZ SANCHEZ</t>
+          <t>A. QUIROS LOPEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6987</v>
+        <v>0.4304</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9061</v>
+        <v>-0.1467</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.2074</v>
+        <v>0.5770999999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>-2.2322</v>
+        <v>-0.2908</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.0028</v>
+        <v>-0.0253</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.2295</v>
+        <v>-0.2656</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.5385</v>
+        <v>0.0403</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0562</v>
+        <v>0.0403</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.5948</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.6937</v>
+        <v>-0.3312</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.059</v>
+        <v>-0.06560000000000001</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.6347</v>
+        <v>-0.2656</v>
       </c>
       <c r="P3" t="n">
-        <v>2.3806</v>
+        <v>0.1984</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.3806</v>
+        <v>0.1984</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2131</v>
+        <v>-0.1516</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2382</v>
+        <v>-0.187</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0251</v>
+        <v>0.0354</v>
       </c>
       <c r="V3" t="n">
-        <v>0.3373</v>
+        <v>0.6745</v>
       </c>
       <c r="W3" t="n">
-        <v>1.2065</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.8692</v>
+        <v>0.6745</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. QUIROS LOPEZ</t>
+          <t>R. DIAZ SANCHEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5145999999999999</v>
+        <v>0.1682</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.1467</v>
+        <v>0.6</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6613</v>
+        <v>-0.4318</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.2908</v>
+        <v>-2.2322</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.0253</v>
+        <v>-1.0028</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2656</v>
+        <v>-1.2295</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0403</v>
+        <v>-0.5385</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0403</v>
+        <v>0.0562</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>-0.5948</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.3312</v>
+        <v>-1.6937</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.06560000000000001</v>
+        <v>-1.059</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.2656</v>
+        <v>-0.6347</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1984</v>
+        <v>2.3806</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.1984</v>
+        <v>2.3806</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0675</v>
+        <v>-0.3174</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.187</v>
+        <v>-0.0679</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1196</v>
+        <v>-0.2495</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6745</v>
+        <v>0.3373</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.2065</v>
       </c>
       <c r="X4" t="n">
-        <v>0.6745</v>
+        <v>-0.8692</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. GAVALDA GUILLEN</t>
+          <t>X. ASSALIT GARCÍA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0456</v>
+        <v>-0.1716</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8935</v>
+        <v>0.956</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.9391</v>
+        <v>-1.1276</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2912</v>
+        <v>-0.4507</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.0507</v>
+        <v>0.3279</v>
       </c>
       <c r="I5" t="n">
-        <v>0.342</v>
+        <v>-0.7786</v>
       </c>
       <c r="J5" t="n">
-        <v>3.0077</v>
+        <v>1.2657</v>
       </c>
       <c r="K5" t="n">
-        <v>1.3508</v>
+        <v>1.2606</v>
       </c>
       <c r="L5" t="n">
-        <v>1.6568</v>
+        <v>0.0051</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.7164</v>
+        <v>-1.7165</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.4015</v>
+        <v>-0.9327</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.3149</v>
+        <v>-0.7837</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5952</v>
+        <v>0.1984</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9919</v>
+        <v>-1.1903</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5871</v>
+        <v>1.3887</v>
       </c>
       <c r="S5" t="n">
-        <v>-2.015</v>
+        <v>0.418</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.1222</v>
+        <v>0.0114</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.8928</v>
+        <v>0.4066</v>
       </c>
       <c r="V5" t="n">
-        <v>1.083</v>
+        <v>-0.3373</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.8692</v>
       </c>
       <c r="X5" t="n">
-        <v>1.083</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X. ASSALIT GARCÍA</t>
+          <t>B. BORRERO PERLAZA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.3476</v>
+        <v>-0.6475</v>
       </c>
       <c r="E6" t="n">
-        <v>0.752</v>
+        <v>-1.6049</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.0996</v>
+        <v>0.9574</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.4507</v>
+        <v>-1.4505</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3279</v>
+        <v>-1.0529</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.7786</v>
+        <v>-0.3977</v>
       </c>
       <c r="J6" t="n">
-        <v>1.2657</v>
+        <v>-0.2668</v>
       </c>
       <c r="K6" t="n">
-        <v>1.2606</v>
+        <v>-0.3873</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0051</v>
+        <v>0.1205</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.7165</v>
+        <v>-1.1837</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.9327</v>
+        <v>-0.6655</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.7837</v>
+        <v>-0.5182</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1984</v>
+        <v>0.3968</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1903</v>
+        <v>-1.9838</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3887</v>
+        <v>2.3806</v>
       </c>
       <c r="S6" t="n">
-        <v>0.242</v>
+        <v>0.1403</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1926</v>
+        <v>0.3798</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4347</v>
+        <v>-0.2395</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.3373</v>
+        <v>0.266</v>
       </c>
       <c r="W6" t="n">
-        <v>0.8692</v>
+        <v>0.266</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.2065</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.8417</v>
+        <v>-1.1019</v>
       </c>
       <c r="E7" t="n">
-        <v>1.8717</v>
+        <v>1.6677</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.7134</v>
+        <v>-2.7695</v>
       </c>
       <c r="G7" t="n">
         <v>-1.2913</v>
@@ -1000,13 +1000,13 @@
         <v>0.3968</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0147</v>
+        <v>-0.2749</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1758</v>
+        <v>-0.0282</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1905</v>
+        <v>-0.2467</v>
       </c>
       <c r="V7" t="n">
         <v>0.266</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.3169</v>
+        <v>-1.7505</v>
       </c>
       <c r="E8" t="n">
-        <v>1.0011</v>
+        <v>0.2869</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.318</v>
+        <v>-2.0375</v>
       </c>
       <c r="G8" t="n">
         <v>-1.7275</v>
@@ -1078,13 +1078,13 @@
         <v>1.9838</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1926</v>
+        <v>-0.6263</v>
       </c>
       <c r="T8" t="n">
-        <v>0.669</v>
+        <v>-0.0452</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.8616</v>
+        <v>-0.5810999999999999</v>
       </c>
       <c r="V8" t="n">
         <v>0.6032</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.7113</v>
+        <v>-2.5981</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.8371</v>
+        <v>-1.0606</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.8741</v>
+        <v>-1.5375</v>
       </c>
       <c r="G9" t="n">
         <v>-1.8527</v>
@@ -1156,13 +1156,13 @@
         <v>2.579</v>
       </c>
       <c r="S9" t="n">
-        <v>-2.5926</v>
+        <v>-1.4794</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.2469</v>
+        <v>-0.4704</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.3457</v>
+        <v>-1.009</v>
       </c>
       <c r="V9" t="n">
         <v>0.3373</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.393</v>
+        <v>-3.8384</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.746</v>
+        <v>-1.2755</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.647</v>
+        <v>-2.5629</v>
       </c>
       <c r="G10" t="n">
         <v>-2.0042</v>
@@ -1234,13 +1234,13 @@
         <v>0.5952</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.9245</v>
+        <v>-0.3698</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7481</v>
+        <v>-0.2777</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1763</v>
+        <v>-0.0922</v>
       </c>
       <c r="V10" t="n">
         <v>-0.8692</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.6357</v>
+        <v>-4.2596</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.788</v>
+        <v>-2.2155</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.8478</v>
+        <v>-2.0442</v>
       </c>
       <c r="G11" t="n">
         <v>-2.8335</v>
@@ -1312,13 +1312,13 @@
         <v>1.3887</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7942</v>
+        <v>-0.4181</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.9975000000000001</v>
+        <v>-0.425</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2034</v>
+        <v>0.007</v>
       </c>
       <c r="V11" t="n">
         <v>-1.2065</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-13.3115</v>
+        <v>-12.9998</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.5363</v>
+        <v>-1.2246</v>
       </c>
       <c r="F12" t="n">
-        <v>-11.7752</v>
+        <v>-11.7753</v>
       </c>
       <c r="G12" t="n">
         <v>-13.8422</v>
@@ -1378,7 +1378,7 @@
         <v>-11.6468</v>
       </c>
       <c r="O12" t="n">
-        <v>-9.165299999999998</v>
+        <v>-9.1653</v>
       </c>
       <c r="P12" t="n">
         <v>3.967799999999999</v>
@@ -1390,13 +1390,13 @@
         <v>14.8789</v>
       </c>
       <c r="S12" t="n">
-        <v>-4.591200000000001</v>
+        <v>-4.2794</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.8695</v>
+        <v>-1.5579</v>
       </c>
       <c r="U12" t="n">
-        <v>-2.7213</v>
+        <v>-2.7215</v>
       </c>
       <c r="V12" t="n">
         <v>1.154299999999999</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>10.1811</v>
+        <v>9.0486</v>
       </c>
       <c r="E13" t="n">
-        <v>9.695499999999999</v>
+        <v>8.6752</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4857</v>
+        <v>0.3735</v>
       </c>
       <c r="G13" t="n">
         <v>5.2891</v>
@@ -1468,13 +1468,13 @@
         <v>1.1903</v>
       </c>
       <c r="S13" t="n">
-        <v>2.7649</v>
+        <v>1.6324</v>
       </c>
       <c r="T13" t="n">
-        <v>2.4035</v>
+        <v>1.3832</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3615</v>
+        <v>0.2492</v>
       </c>
       <c r="V13" t="n">
         <v>1.1352</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.6805</v>
+        <v>7.9254</v>
       </c>
       <c r="E14" t="n">
-        <v>7.0548</v>
+        <v>6.8507</v>
       </c>
       <c r="F14" t="n">
-        <v>0.6258</v>
+        <v>1.0747</v>
       </c>
       <c r="G14" t="n">
         <v>3.8574</v>
@@ -1546,13 +1546,13 @@
         <v>1.7855</v>
       </c>
       <c r="S14" t="n">
-        <v>0.8151</v>
+        <v>1.0599</v>
       </c>
       <c r="T14" t="n">
-        <v>1.2301</v>
+        <v>1.026</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.415</v>
+        <v>0.0339</v>
       </c>
       <c r="V14" t="n">
         <v>2.4129</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.8362</v>
+        <v>5.076</v>
       </c>
       <c r="E15" t="n">
-        <v>4.5964</v>
+        <v>5.0046</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2398</v>
+        <v>0.07149999999999999</v>
       </c>
       <c r="G15" t="n">
         <v>2.7582</v>
@@ -1624,13 +1624,13 @@
         <v>1.7855</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5622</v>
+        <v>0.802</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2382</v>
+        <v>0.6463</v>
       </c>
       <c r="U15" t="n">
-        <v>0.324</v>
+        <v>0.1557</v>
       </c>
       <c r="V15" t="n">
         <v>-0.0713</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.1409</v>
+        <v>4.401</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9546</v>
+        <v>2.383</v>
       </c>
       <c r="F16" t="n">
-        <v>2.1863</v>
+        <v>2.018</v>
       </c>
       <c r="G16" t="n">
         <v>4.4776</v>
@@ -1702,13 +1702,13 @@
         <v>1.7855</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2654</v>
+        <v>0.9947</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.9975000000000001</v>
+        <v>0.4309</v>
       </c>
       <c r="U16" t="n">
-        <v>0.7322</v>
+        <v>0.5638</v>
       </c>
       <c r="V16" t="n">
         <v>-0.6745</v>
@@ -1735,10 +1735,10 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9922</v>
+        <v>0.6862</v>
       </c>
       <c r="E17" t="n">
-        <v>0.3144</v>
+        <v>0.0083</v>
       </c>
       <c r="F17" t="n">
         <v>0.6778999999999999</v>
@@ -1780,10 +1780,10 @@
         <v>1.3887</v>
       </c>
       <c r="S17" t="n">
-        <v>0.7425</v>
+        <v>0.4365</v>
       </c>
       <c r="T17" t="n">
-        <v>0.4876</v>
+        <v>0.1815</v>
       </c>
       <c r="U17" t="n">
         <v>0.255</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1327</v>
+        <v>-0.4847</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.3986</v>
+        <v>-1.8067</v>
       </c>
       <c r="F18" t="n">
-        <v>1.2659</v>
+        <v>1.322</v>
       </c>
       <c r="G18" t="n">
         <v>-0.8649</v>
@@ -1858,13 +1858,13 @@
         <v>1.5871</v>
       </c>
       <c r="S18" t="n">
-        <v>0.9387</v>
+        <v>0.5867</v>
       </c>
       <c r="T18" t="n">
-        <v>0.4876</v>
+        <v>0.0794</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4511</v>
+        <v>0.5072</v>
       </c>
       <c r="V18" t="n">
         <v>-0.6032</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.9831</v>
+        <v>-0.9651999999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.5043</v>
+        <v>-0.4023</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.4788</v>
+        <v>-0.5629</v>
       </c>
       <c r="G19" t="n">
         <v>-0.6435999999999999</v>
@@ -1936,13 +1936,13 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3395</v>
+        <v>-0.3217</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.187</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1525</v>
+        <v>-0.2367</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.775</v>
+        <v>-1.8311</v>
       </c>
       <c r="E20" t="n">
         <v>-1.7162</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.0588</v>
+        <v>-0.1149</v>
       </c>
       <c r="G20" t="n">
         <v>0.8414</v>
@@ -2014,13 +2014,13 @@
         <v>0.3968</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0374</v>
+        <v>-0.0935</v>
       </c>
       <c r="T20" t="n">
         <v>-0.3117</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2743</v>
+        <v>0.2182</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.0447</v>
+        <v>-2.1008</v>
       </c>
       <c r="E21" t="n">
         <v>-2.2518</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2072</v>
+        <v>0.1511</v>
       </c>
       <c r="G21" t="n">
         <v>-2.404</v>
@@ -2092,13 +2092,13 @@
         <v>0.3968</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0374</v>
+        <v>-0.0935</v>
       </c>
       <c r="T21" t="n">
         <v>-0.3117</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2743</v>
+        <v>0.2182</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>R. DE LEON</t>
+          <t>A. MONTALBÁN PÉREZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.0595</v>
+        <v>-4.0962</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.4986</v>
+        <v>-1.2667</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.5609</v>
+        <v>-2.8294</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.7333</v>
+        <v>0.4196</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.6906</v>
+        <v>-0.1918</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.0427</v>
+        <v>0.6115</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.2168</v>
+        <v>0.9329</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.2971</v>
+        <v>1.0081</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0803</v>
+        <v>-0.0752</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.5165</v>
+        <v>-0.5132</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.3935</v>
+        <v>-1.1999</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.123</v>
+        <v>0.6867</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.7774</v>
+        <v>-1.5871</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.9758</v>
+        <v>-1.9838</v>
       </c>
       <c r="R22" t="n">
-        <v>0.1984</v>
+        <v>0.3968</v>
       </c>
       <c r="S22" t="n">
-        <v>0.3917</v>
+        <v>-0.5158</v>
       </c>
       <c r="T22" t="n">
-        <v>0.3685</v>
+        <v>-0.4817</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0232</v>
+        <v>-0.034</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.9405</v>
+        <v>-2.4129</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.6745</v>
+        <v>0.266</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.266</v>
+        <v>-2.6789</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. MONTALBÁN PÉREZ</t>
+          <t>R. DE LEON</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.5247</v>
+        <v>-4.3477</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.4708</v>
+        <v>-3.7027</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.0539</v>
+        <v>-0.6451</v>
       </c>
       <c r="G23" t="n">
-        <v>0.4196</v>
+        <v>-0.7333</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.1918</v>
+        <v>-0.6906</v>
       </c>
       <c r="I23" t="n">
-        <v>0.6115</v>
+        <v>-0.0427</v>
       </c>
       <c r="J23" t="n">
-        <v>0.9329</v>
+        <v>-0.2168</v>
       </c>
       <c r="K23" t="n">
-        <v>1.0081</v>
+        <v>-0.2971</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.0752</v>
+        <v>0.0803</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.5132</v>
+        <v>-0.5165</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.1999</v>
+        <v>-0.3935</v>
       </c>
       <c r="O23" t="n">
-        <v>0.6867</v>
+        <v>-0.123</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.5871</v>
+        <v>-2.7774</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.9838</v>
+        <v>-2.9758</v>
       </c>
       <c r="R23" t="n">
-        <v>0.3968</v>
+        <v>0.1984</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.9443</v>
+        <v>0.1034</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6858</v>
+        <v>0.1644</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2585</v>
+        <v>-0.061</v>
       </c>
       <c r="V23" t="n">
-        <v>-2.4129</v>
+        <v>-0.9405</v>
       </c>
       <c r="W23" t="n">
-        <v>0.266</v>
+        <v>-0.6745</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.6789</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>13.31120000000001</v>
+        <v>13.3115</v>
       </c>
       <c r="E24" t="n">
         <v>11.7754</v>
       </c>
       <c r="F24" t="n">
-        <v>1.5362</v>
+        <v>1.536399999999999</v>
       </c>
       <c r="G24" t="n">
         <v>13.8424</v>
@@ -2326,13 +2326,13 @@
         <v>10.9114</v>
       </c>
       <c r="S24" t="n">
-        <v>4.591100000000001</v>
+        <v>4.591100000000002</v>
       </c>
       <c r="T24" t="n">
-        <v>2.7218</v>
+        <v>2.7216</v>
       </c>
       <c r="U24" t="n">
-        <v>1.8696</v>
+        <v>1.8695</v>
       </c>
       <c r="V24" t="n">
         <v>-1.154300000000001</v>
